--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/NEW_MEXICO_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/NEW_MEXICO_2011.xlsx
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C120">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C162">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C194">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C524">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C793">
